--- a/raw/trektellen/Trektellen_headerdata_2422_2026.xlsx
+++ b/raw/trektellen/Trektellen_headerdata_2422_2026.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="583">
   <si>
     <t>id</t>
   </si>
@@ -1556,13 +1556,214 @@
     <t>2026-10-01 19:17:00</t>
   </si>
   <si>
-    <t xml:space="preserve">Tilian Molnar, Maxence </t>
+    <t>Tilian Molnar, Maxence Deveze</t>
   </si>
   <si>
     <t xml:space="preserve">Pas de stratus sur le Rhône le matin. Vent S2. Nébulosité basse 8/8. 16 degrés. Légères averses de 10h à 14h. Puis HP de 14h45 au coucher du soleil. Pluie forte sans arrêt. </t>
   </si>
   <si>
+    <t>Mis à part quelques passereaux et hirondelles, le monde n'est pas motivé à voyager. Pas étonnant au vu de la météo peu clémente du jour... L'après-midi était complètement bouchée, pluie pluie pluie... Demain ça débloque, y'a plus qu'à !</t>
+  </si>
+  <si>
     <t>2026-10-01 21:49:26.393097</t>
+  </si>
+  <si>
+    <t>2026-10-01 21:53:12.428876</t>
+  </si>
+  <si>
+    <t>2026-10-02 07:36:00</t>
+  </si>
+  <si>
+    <t>2026-10-02 19:15:00</t>
+  </si>
+  <si>
+    <t>Tilian Molnar, Tiphaine Causse, Benjamin Bruno, Maxence Deveze, Alicia Duclosson, Daniel Comte, Stephen Henneberg, Vincent Mathez, Martine Michel, Timothée Habert, Dany Goujon, Catherine Dombray,</t>
+  </si>
+  <si>
+    <t>Stratus sur le Rhône jusqu&amp;#039;à 8h30. Vent NE faible à modéré. Nébulosité basse de cumulostratus 8/8. 19°C</t>
+  </si>
+  <si>
+    <t>Enfin une journée digne du Défilé ! Malgré une attente élevée, nous n'avons pas été déçu du passage de nos oiseaux migrateurs ! Une activité tout au long de la journée avec des observations qui régale les yeux ! Les bénévoles ont répondus présent et ont bien aidé pour les détections parfois hasardeuses ! Des flux un peu dans tous les sens mais c'est ça qu'on aime, de la belle migration. On peut le dire quand même pour la première fois de la saison et véridique : VIVA L'ÉCLUSE !!!</t>
+  </si>
+  <si>
+    <t>2026-10-02 19:40:40.388291</t>
+  </si>
+  <si>
+    <t>2026-10-02 20:08:19.980081</t>
+  </si>
+  <si>
+    <t>2026-10-03 07:37:00</t>
+  </si>
+  <si>
+    <t>2026-10-03 19:13:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tilian Molnar, Tiphaine Causse, Camille Legrand, Élisa Fage, Isabelle &amp;amp; Roger Cattin-Gasser, Luc Moreau, Claude Marot </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stratus sur le Rhône le matin. Nébulosité haute de Stratocumulus 7/8. 19°C. Vent de NE assez faible. </t>
+  </si>
+  <si>
+    <t>Comment décrire cette matinée hors du commun, qui de par sa belle diversité de passereaux nous rappelle que nous sommes bien en octobre, il était temps ! Les mouvements matinaux étaient assez haut dans le ciel, mais la nébulosité a permis la détection de bon nombre d'entre eux. Ces petits grelots d'accenteurs crééent déjà de belles ambiances. Mais tout a basculé lorsque ce piaf étrange fit son apparition côté Salève. Premier coup d'oeil : de bien longues rectrices, corps trapu, ailes larges et vol puissant. Sans oublier ses gros placards blancs. Quelques secondes d'hésitation. C'est quoi ce machin ? Un perroquet ? Oui oui la réflexion fut réalisée. Mais dès que l'oiseau se rapproche, l'hésitation est vite envolée : une Pie-grièche grise !!! Un mythe, une légende, un monde lointain dans mon imaginaire... Et pourtant, le voilà bel et bien en migration active ! Quel pied ! Mais l'histoire ne s'arrête pas là, lorsque quelques petites heures plus tard un autre oiseau se pointe à l'intersection. Aux jumelles, un jizz de grive. Dans la longue-vue l'histoire s'écrit. Avec ce 2ème individu de Pie-grièche grise : passant cette fois en fond de végétation, passant fond de Défilé. Oui, cette matinée est complètement folle, des obs récompensant cette saison pour le moins calme... Évidemment, les rapaces aussi ont leur place dans le commentaire du jour, volant très peu ce matin, ils ont su prendre le relais dans un timing bien précis !</t>
+  </si>
+  <si>
+    <t>2026-10-03 19:33:12.198954</t>
+  </si>
+  <si>
+    <t>2026-10-03 19:54:04.422899</t>
+  </si>
+  <si>
+    <t>2026-10-04 07:38:00</t>
+  </si>
+  <si>
+    <t>2026-10-04 19:16:00</t>
+  </si>
+  <si>
+    <t>Des oiseaux pour l'eurobirdwatch que demandé de plus!! Très bonne ambiance sur le spot et du passage varié et continue, mention spéciale pour les colombins avec la 4ieme meilleurs journée pour le site!! VIVA L'ECLUSE</t>
+  </si>
+  <si>
+    <t>2026-10-04 19:18:14.989851</t>
+  </si>
+  <si>
+    <t>2026-10-13 13:22:40.464069</t>
+  </si>
+  <si>
+    <t>2026-10-05 07:32:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 19:09:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tilian Molnar, Tiphaine Causse, Philippe Roy </t>
+  </si>
+  <si>
+    <t>Stratus sur le Rhône jusqu'à 9h30. Vent de NE modéré. Nébulosité haute de 4/8. 22°C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heureusement que les nuages étaient de la partie, parce que les détections étaient loin ! Une après-midi bien calme et une matinée assez classique de saison. Demain, c'est pire, même journée mais sans nuages ! Y a des yeux qui vont se perdre ! </t>
+  </si>
+  <si>
+    <t>2026-10-05 19:57:05.403537</t>
+  </si>
+  <si>
+    <t>2026-10-06 08:14:00.341253</t>
+  </si>
+  <si>
+    <t>2026-10-06 07:41:00</t>
+  </si>
+  <si>
+    <t>2026-10-06 19:07:00</t>
+  </si>
+  <si>
+    <t>Tiphaine Causse</t>
+  </si>
+  <si>
+    <t>Stratus sur le Rhône jusqu'à 10h15. Cimetière jusqu'à 9h45. Léger vent de Sud. Nébulosité haute avec cumulus 1/8. 23°C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciel bleu 1 / 0 Le T : Digne des plus belles journées d'août, c'est le retour de notre chère et tendre ciel bleu. Qu'est-ce qu'il avait manqué en cette looooongue journée assez pauvre en donnée pour cette date. Quelques nuages ont permis quelques obs inté... Ah non, c'est passé en permanence sur fond de ciel de quoi bien se dégommer la rétine, un pur plaisir ! Notons ce levé de dortoir d'alouettes lulu juste devant le spot secondaire dans une douce lumière d'aurore, ça régale ! </t>
+  </si>
+  <si>
+    <t>2026-10-06 20:06:01.812448</t>
+  </si>
+  <si>
+    <t>2026-10-07 07:42:00</t>
+  </si>
+  <si>
+    <t>2026-10-07 19:05:00</t>
+  </si>
+  <si>
+    <t>Tilian Molnar</t>
+  </si>
+  <si>
+    <t>HP de 11h30 à 13h00 puis de 15h10 à la fin de protocole. Stratus sur le Rhône le matin. Pluie constante de 9h30 à 13h00 puis pluie battante de 15h00 à la fin de protocole. Vent N1. Nébulosité basse 8/8. 14 degrés.</t>
+  </si>
+  <si>
+    <t>Ce matin ça sort les cliqueurs sous la pluie ! Entre les pigeons qui passent avant le rideau de pluie et les pinsons qui passent par paquets sous les gouttes, la matinée fut mouvementée. Sans oublier ces mouvements de grives musiciennes allant à ravir dans ces ambiances automnales. Un petit créneau sans pluie en début d'aprem permer à quelques rapaces de se faire la malle. On peut noter cet Hobereau à la bourre ou ce Balbu sortant du Rhône. Et que serait cette journée sans un petit limi ? Quelle belle donnée que ce Bécasseau variable ! Demain, c'est encore pluie, mais il en faut :)</t>
+  </si>
+  <si>
+    <t>2026-10-07 19:42:55.025448</t>
+  </si>
+  <si>
+    <t>2026-10-08 07:43:00</t>
+  </si>
+  <si>
+    <t>2026-10-08 19:03:00</t>
+  </si>
+  <si>
+    <t>Alors comment vous dire qu'aujourd'hui on s'est fait chier comme des rats crevés... L'avantage c'est que ça passera mieux demain ;)</t>
+  </si>
+  <si>
+    <t>2026-10-08 19:16:13.191892</t>
+  </si>
+  <si>
+    <t>2026-10-09 07:45:00</t>
+  </si>
+  <si>
+    <t>2026-10-09 19:01:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tilian Molnar, Tiphaine Causse, Maeve Briand, Cyann Ménard, Benjamin Bruno, Sylvie Freymond, Lutz Lucker, Vincent Mathez, Martine Michel, Philippe Roy, Jérémy Calvo, Frédéric Bacuez, Élise Faraut </t>
+  </si>
+  <si>
+    <t>Vent N2. Pas de stratus sur le Rhône. Nébulosité basse 7/8. Bonne visibilité.</t>
+  </si>
+  <si>
+    <t>Alors que les Pigeons ne daignent pas passer en force, les rapaces ont su prendre la relève. Enfin des beaux mouvements de Buses, il était temps. La lumière ne nous a pas toujours aidé pour les détails, mais ce n'est que mieux pour réviser les critères ! Merci à tous pour l'aide sur spot, à tout vite pour de nouvelles belles journées :)</t>
+  </si>
+  <si>
+    <t>2026-10-09 19:29:47.518656</t>
+  </si>
+  <si>
+    <t>2026-10-10 07:46:00</t>
+  </si>
+  <si>
+    <t>2026-10-10 19:00:00</t>
+  </si>
+  <si>
+    <t>Tilian Molnar, Tiphaine Causse, Maeve Briand, Cyann Ménard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Léger vent de Sud. Nébulosité haute de cumulostratus et stratus 7/8. Quelques averses légère toute au long de la journée. 13°C. </t>
+  </si>
+  <si>
+    <t>Aujourd'hui est un grand jour ! La mascotte du spot fête ses 1 an ! Yuri grandit petit à petit. Il pensait que tout était permis, alors aujourd'hui il s'est dit que jouer avec les chiens de chasse était une bonne idée :) Plus de temps passé sur les spots de migr que partout ailleurs pour l'instant, la vie est dure... Mis à part les nouvelles de la mascotte, le vent de Sud a permis de voir de beaux petits mouvements migratoires de passereaux, sans qui la matinée aurait été bien longue... Un jeune Busard pâle overhead a lancé une bien courte dynamique rapaces. Un émerillon nous rase la casquette. La matinée ne fut pas triste ! Quant à l'aprem, pas besoin de longs discours...</t>
+  </si>
+  <si>
+    <t>2026-10-10 19:48:02.836487</t>
+  </si>
+  <si>
+    <t>2026-10-11 07:46:00</t>
+  </si>
+  <si>
+    <t>2026-10-11 18:56:13</t>
+  </si>
+  <si>
+    <t>Dominique Maire, Pascal Charrière, Lutz Lucker</t>
+  </si>
+  <si>
+    <t>couvert</t>
+  </si>
+  <si>
+    <t>2026-10-11 18:56:13.375959</t>
+  </si>
+  <si>
+    <t>2026-10-12 07:49:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 18:56:00</t>
+  </si>
+  <si>
+    <t>Tilian Molnar, Tiphaine Causse, Maeve Briand, Cyann Ménard, Raymond Bedouet</t>
+  </si>
+  <si>
+    <t>Stratus sur le Rhône jusqu'à 10h. Vent NNE2. Nébulosité haute 1/8. 15 degrés. Bonne visibilité.</t>
+  </si>
+  <si>
+    <t>Alors que la matinée fut mouvementée par les pigeons et les cormorans, l'aprem fut finalement assez riche en rapaces ! Notamment de beaux trains trains de Buses et Milans. Pas facile à trouver dans le ciel bleu mais en fin de journée de jolis passages continueront jusqu'à 30 mn avant le coucher de soleil !</t>
+  </si>
+  <si>
+    <t>2026-10-12 19:20:10.264056</t>
   </si>
 </sst>
 </file>
@@ -1901,7 +2102,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AD77"/>
+  <dimension ref="A1:AD88"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:30">
@@ -7256,14 +7457,714 @@
       <c r="Y77" t="s">
         <v>34</v>
       </c>
+      <c r="Z77" t="s">
+        <v>515</v>
+      </c>
       <c r="AA77" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AB77" t="s">
         <v>37</v>
       </c>
       <c r="AC77" t="s">
-        <v>515</v>
+        <v>517</v>
+      </c>
+      <c r="AD77" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="78" spans="1:30">
+      <c r="A78">
+        <v>3590753</v>
+      </c>
+      <c r="B78">
+        <v>2422</v>
+      </c>
+      <c r="C78">
+        <v>40</v>
+      </c>
+      <c r="D78">
+        <v>5</v>
+      </c>
+      <c r="E78">
+        <v>2</v>
+      </c>
+      <c r="F78">
+        <v>10</v>
+      </c>
+      <c r="G78">
+        <v>2026</v>
+      </c>
+      <c r="H78" t="s">
+        <v>518</v>
+      </c>
+      <c r="I78" t="s">
+        <v>519</v>
+      </c>
+      <c r="J78" t="s">
+        <v>520</v>
+      </c>
+      <c r="K78" t="s">
+        <v>521</v>
+      </c>
+      <c r="L78">
+        <v>3</v>
+      </c>
+      <c r="M78">
+        <v>4</v>
+      </c>
+      <c r="N78" t="s">
+        <v>130</v>
+      </c>
+      <c r="O78">
+        <v>8</v>
+      </c>
+      <c r="P78">
+        <v>1800</v>
+      </c>
+      <c r="S78">
+        <v>7000</v>
+      </c>
+      <c r="T78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>3</v>
+      </c>
+      <c r="X78">
+        <v>12</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>522</v>
+      </c>
+      <c r="AA78" t="s">
+        <v>523</v>
+      </c>
+      <c r="AB78" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC78" t="s">
+        <v>524</v>
+      </c>
+      <c r="AD78" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="79" spans="1:30">
+      <c r="A79">
+        <v>3595350</v>
+      </c>
+      <c r="B79">
+        <v>2422</v>
+      </c>
+      <c r="C79">
+        <v>40</v>
+      </c>
+      <c r="D79">
+        <v>6</v>
+      </c>
+      <c r="E79">
+        <v>3</v>
+      </c>
+      <c r="F79">
+        <v>10</v>
+      </c>
+      <c r="G79">
+        <v>2026</v>
+      </c>
+      <c r="H79" t="s">
+        <v>525</v>
+      </c>
+      <c r="I79" t="s">
+        <v>526</v>
+      </c>
+      <c r="J79" t="s">
+        <v>527</v>
+      </c>
+      <c r="K79" t="s">
+        <v>528</v>
+      </c>
+      <c r="P79">
+        <v>5000</v>
+      </c>
+      <c r="S79">
+        <v>5000</v>
+      </c>
+      <c r="T79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>1</v>
+      </c>
+      <c r="X79">
+        <v>8</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>529</v>
+      </c>
+      <c r="AA79" t="s">
+        <v>530</v>
+      </c>
+      <c r="AB79" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC79" t="s">
+        <v>531</v>
+      </c>
+      <c r="AD79" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="80" spans="1:30">
+      <c r="A80">
+        <v>3598264</v>
+      </c>
+      <c r="B80">
+        <v>2422</v>
+      </c>
+      <c r="C80">
+        <v>40</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>4</v>
+      </c>
+      <c r="F80">
+        <v>10</v>
+      </c>
+      <c r="G80">
+        <v>2026</v>
+      </c>
+      <c r="H80" t="s">
+        <v>532</v>
+      </c>
+      <c r="I80" t="s">
+        <v>533</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="S80">
+        <v>0</v>
+      </c>
+      <c r="T80">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>534</v>
+      </c>
+      <c r="AA80" t="s">
+        <v>535</v>
+      </c>
+      <c r="AB80" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC80" t="s">
+        <v>536</v>
+      </c>
+      <c r="AD80" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="81" spans="1:30">
+      <c r="A81">
+        <v>3600637</v>
+      </c>
+      <c r="B81">
+        <v>2422</v>
+      </c>
+      <c r="C81">
+        <v>40</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81">
+        <v>5</v>
+      </c>
+      <c r="F81">
+        <v>10</v>
+      </c>
+      <c r="G81">
+        <v>2026</v>
+      </c>
+      <c r="H81" t="s">
+        <v>537</v>
+      </c>
+      <c r="I81" t="s">
+        <v>538</v>
+      </c>
+      <c r="J81" t="s">
+        <v>539</v>
+      </c>
+      <c r="K81" t="s">
+        <v>540</v>
+      </c>
+      <c r="P81">
+        <v>8000</v>
+      </c>
+      <c r="S81">
+        <v>6000</v>
+      </c>
+      <c r="T81">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>1</v>
+      </c>
+      <c r="X81">
+        <v>3</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>541</v>
+      </c>
+      <c r="AA81" t="s">
+        <v>542</v>
+      </c>
+      <c r="AB81" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC81" t="s">
+        <v>543</v>
+      </c>
+      <c r="AD81" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="82" spans="1:30">
+      <c r="A82">
+        <v>3603247</v>
+      </c>
+      <c r="B82">
+        <v>2422</v>
+      </c>
+      <c r="C82">
+        <v>40</v>
+      </c>
+      <c r="D82">
+        <v>2</v>
+      </c>
+      <c r="E82">
+        <v>6</v>
+      </c>
+      <c r="F82">
+        <v>10</v>
+      </c>
+      <c r="G82">
+        <v>2026</v>
+      </c>
+      <c r="H82" t="s">
+        <v>544</v>
+      </c>
+      <c r="I82" t="s">
+        <v>545</v>
+      </c>
+      <c r="J82" t="s">
+        <v>546</v>
+      </c>
+      <c r="K82" t="s">
+        <v>547</v>
+      </c>
+      <c r="P82">
+        <v>6000</v>
+      </c>
+      <c r="S82">
+        <v>7000</v>
+      </c>
+      <c r="T82">
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <v>1</v>
+      </c>
+      <c r="X82">
+        <v>1</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>548</v>
+      </c>
+      <c r="AA82" t="s">
+        <v>549</v>
+      </c>
+      <c r="AB82" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC82" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="83" spans="1:30">
+      <c r="A83">
+        <v>3606864</v>
+      </c>
+      <c r="B83">
+        <v>2422</v>
+      </c>
+      <c r="C83">
+        <v>40</v>
+      </c>
+      <c r="D83">
+        <v>3</v>
+      </c>
+      <c r="E83">
+        <v>7</v>
+      </c>
+      <c r="F83">
+        <v>10</v>
+      </c>
+      <c r="G83">
+        <v>2026</v>
+      </c>
+      <c r="H83" t="s">
+        <v>550</v>
+      </c>
+      <c r="I83" t="s">
+        <v>551</v>
+      </c>
+      <c r="J83" t="s">
+        <v>552</v>
+      </c>
+      <c r="K83" t="s">
+        <v>553</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="S83">
+        <v>0</v>
+      </c>
+      <c r="T83">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>554</v>
+      </c>
+      <c r="AA83" t="s">
+        <v>555</v>
+      </c>
+      <c r="AB83" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC83" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="84" spans="1:30">
+      <c r="A84">
+        <v>3608654</v>
+      </c>
+      <c r="B84">
+        <v>2422</v>
+      </c>
+      <c r="C84">
+        <v>41</v>
+      </c>
+      <c r="D84">
+        <v>4</v>
+      </c>
+      <c r="E84">
+        <v>8</v>
+      </c>
+      <c r="F84">
+        <v>10</v>
+      </c>
+      <c r="G84">
+        <v>2026</v>
+      </c>
+      <c r="H84" t="s">
+        <v>556</v>
+      </c>
+      <c r="I84" t="s">
+        <v>557</v>
+      </c>
+      <c r="J84" t="s">
+        <v>53</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="S84">
+        <v>0</v>
+      </c>
+      <c r="T84">
+        <v>0</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>558</v>
+      </c>
+      <c r="AA84" t="s">
+        <v>559</v>
+      </c>
+      <c r="AB84" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC84" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="85" spans="1:30">
+      <c r="A85">
+        <v>3610603</v>
+      </c>
+      <c r="B85">
+        <v>2422</v>
+      </c>
+      <c r="C85">
+        <v>41</v>
+      </c>
+      <c r="D85">
+        <v>5</v>
+      </c>
+      <c r="E85">
+        <v>9</v>
+      </c>
+      <c r="F85">
+        <v>10</v>
+      </c>
+      <c r="G85">
+        <v>2026</v>
+      </c>
+      <c r="H85" t="s">
+        <v>560</v>
+      </c>
+      <c r="I85" t="s">
+        <v>561</v>
+      </c>
+      <c r="J85" t="s">
+        <v>562</v>
+      </c>
+      <c r="K85" t="s">
+        <v>563</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="S85">
+        <v>0</v>
+      </c>
+      <c r="T85">
+        <v>0</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>564</v>
+      </c>
+      <c r="AA85" t="s">
+        <v>565</v>
+      </c>
+      <c r="AB85" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC85" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="86" spans="1:30">
+      <c r="A86">
+        <v>3613023</v>
+      </c>
+      <c r="B86">
+        <v>2422</v>
+      </c>
+      <c r="C86">
+        <v>41</v>
+      </c>
+      <c r="D86">
+        <v>6</v>
+      </c>
+      <c r="E86">
+        <v>10</v>
+      </c>
+      <c r="F86">
+        <v>10</v>
+      </c>
+      <c r="G86">
+        <v>2026</v>
+      </c>
+      <c r="H86" t="s">
+        <v>566</v>
+      </c>
+      <c r="I86" t="s">
+        <v>567</v>
+      </c>
+      <c r="J86" t="s">
+        <v>568</v>
+      </c>
+      <c r="K86" t="s">
+        <v>569</v>
+      </c>
+      <c r="P86">
+        <v>2000</v>
+      </c>
+      <c r="S86">
+        <v>5000</v>
+      </c>
+      <c r="T86">
+        <v>0</v>
+      </c>
+      <c r="W86">
+        <v>2</v>
+      </c>
+      <c r="X86">
+        <v>6</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>570</v>
+      </c>
+      <c r="AA86" t="s">
+        <v>571</v>
+      </c>
+      <c r="AB86" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC86" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="87" spans="1:30">
+      <c r="A87">
+        <v>3614808</v>
+      </c>
+      <c r="B87">
+        <v>2422</v>
+      </c>
+      <c r="C87">
+        <v>41</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>11</v>
+      </c>
+      <c r="F87">
+        <v>10</v>
+      </c>
+      <c r="G87">
+        <v>2026</v>
+      </c>
+      <c r="H87" t="s">
+        <v>572</v>
+      </c>
+      <c r="I87" t="s">
+        <v>573</v>
+      </c>
+      <c r="J87" t="s">
+        <v>574</v>
+      </c>
+      <c r="K87" t="s">
+        <v>575</v>
+      </c>
+      <c r="O87">
+        <v>6</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="S87">
+        <v>0</v>
+      </c>
+      <c r="T87">
+        <v>0</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA87" t="s">
+        <v>576</v>
+      </c>
+      <c r="AB87" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC87" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="88" spans="1:30">
+      <c r="A88">
+        <v>3616882</v>
+      </c>
+      <c r="B88">
+        <v>2422</v>
+      </c>
+      <c r="C88">
+        <v>41</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="E88">
+        <v>12</v>
+      </c>
+      <c r="F88">
+        <v>10</v>
+      </c>
+      <c r="G88">
+        <v>2026</v>
+      </c>
+      <c r="H88" t="s">
+        <v>577</v>
+      </c>
+      <c r="I88" t="s">
+        <v>578</v>
+      </c>
+      <c r="J88" t="s">
+        <v>579</v>
+      </c>
+      <c r="K88" t="s">
+        <v>580</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="S88">
+        <v>0</v>
+      </c>
+      <c r="T88">
+        <v>0</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>581</v>
+      </c>
+      <c r="AA88" t="s">
+        <v>582</v>
+      </c>
+      <c r="AB88" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC88" t="s">
+        <v>582</v>
       </c>
     </row>
   </sheetData>

--- a/raw/trektellen/Trektellen_headerdata_2422_2026.xlsx
+++ b/raw/trektellen/Trektellen_headerdata_2422_2026.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="602">
   <si>
     <t>id</t>
   </si>
@@ -1764,6 +1764,63 @@
   </si>
   <si>
     <t>2026-10-12 19:20:10.264056</t>
+  </si>
+  <si>
+    <t>2026-10-13 07:50:00</t>
+  </si>
+  <si>
+    <t>2026-10-13 18:54:00</t>
+  </si>
+  <si>
+    <t>Tilian Molnar, Tiphaine Causse, Maeve Briand, Cyann Ménard,</t>
+  </si>
+  <si>
+    <t>Cimetière jusqu'à 10h. Stratus sur le Rhône jusqu'à 11h30. Vent modéré d'Est. Nébulosité haute et basse de 8/8 avec stratocumulus et stratus. 18°C.</t>
+  </si>
+  <si>
+    <t>Une belle journée d'octobre avec sa diversité, ses quantités et ses ambiances de lumière et de couleur ! Les pigeons passent, les pèlerins fondent tels des fusées sur leurs proies... Les attaques prodigieuses tendent souvent à des échecs... Mais parfois, une nuée de plumes s'observent à la longue-vue. Les passereaux passerotent à grande hauteurs, les cormorans se cormorans dessus partout dans la sphère et les étourneaux, dans leurs balais incessant de migration, se migrent dessus !</t>
+  </si>
+  <si>
+    <t>2026-10-13 19:58:45.997572</t>
+  </si>
+  <si>
+    <t>2026-10-13 20:07:41.028641</t>
+  </si>
+  <si>
+    <t>2026-10-14 07:52:00</t>
+  </si>
+  <si>
+    <t>2026-10-14 18:52:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiphaine Causse, Maeve Briand, Cyann Ménard, Isabelle Cattin-Gasser </t>
+  </si>
+  <si>
+    <t>Stratus sur le Rhône jusqu'à 11h00. Nébulosité haute de Cirrus et Cirrostratus 3/8. Vent N à NE faible. 19°C.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quiet day but what flock my friend ! Une matinée qui démarre treeees lentement. Une partie de la matinée s'est déroulé sous les stratus laissant place à de chouettes ambiances de lumières. Niveau rapaces, la journée n'était pas favorable pour faciliter leurs observations mais nous avons eu des trains trains très agréable et pédagogique ! Demain c'est rebolote, on espère des dynamiques passereaux un peu plus active ! </t>
+  </si>
+  <si>
+    <t>2026-10-14 19:29:22.438287</t>
+  </si>
+  <si>
+    <t>2026-10-15 07:53:00</t>
+  </si>
+  <si>
+    <t>2026-10-15 18:50:00</t>
+  </si>
+  <si>
+    <t>Tilian Molnar, Tiphaine Causse, Cyann Ménard</t>
+  </si>
+  <si>
+    <t>Cimetière jusqu'à 10h30. Stratus sur le Rhône jusqu'à 11h00. Vent N1. Nébulosité haute 5/8. Visibilité moyenne. 18 degrés.</t>
+  </si>
+  <si>
+    <t>Aujourd'hui ça bouge pas des masses... Pourtant il fait beau, peut être trop beau... Un peu de bise l'aprem, mais ça n'a pas l'air de motiver grand monde chez les raptors. On attend le froid !</t>
+  </si>
+  <si>
+    <t>2026-10-15 18:51:53.464504</t>
   </si>
 </sst>
 </file>
@@ -2102,7 +2159,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AD88"/>
+  <dimension ref="A1:AD91"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:30">
@@ -8165,6 +8222,198 @@
       </c>
       <c r="AC88" t="s">
         <v>582</v>
+      </c>
+    </row>
+    <row r="89" spans="1:30">
+      <c r="A89">
+        <v>3619686</v>
+      </c>
+      <c r="B89">
+        <v>2422</v>
+      </c>
+      <c r="C89">
+        <v>41</v>
+      </c>
+      <c r="D89">
+        <v>2</v>
+      </c>
+      <c r="E89">
+        <v>13</v>
+      </c>
+      <c r="F89">
+        <v>10</v>
+      </c>
+      <c r="G89">
+        <v>2026</v>
+      </c>
+      <c r="H89" t="s">
+        <v>583</v>
+      </c>
+      <c r="I89" t="s">
+        <v>584</v>
+      </c>
+      <c r="J89" t="s">
+        <v>585</v>
+      </c>
+      <c r="K89" t="s">
+        <v>586</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="S89">
+        <v>0</v>
+      </c>
+      <c r="T89">
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <v>3</v>
+      </c>
+      <c r="X89">
+        <v>4</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>587</v>
+      </c>
+      <c r="AA89" t="s">
+        <v>588</v>
+      </c>
+      <c r="AB89" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC89" t="s">
+        <v>589</v>
+      </c>
+      <c r="AD89" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="90" spans="1:30">
+      <c r="A90">
+        <v>3623909</v>
+      </c>
+      <c r="B90">
+        <v>2422</v>
+      </c>
+      <c r="C90">
+        <v>41</v>
+      </c>
+      <c r="D90">
+        <v>3</v>
+      </c>
+      <c r="E90">
+        <v>14</v>
+      </c>
+      <c r="F90">
+        <v>10</v>
+      </c>
+      <c r="G90">
+        <v>2026</v>
+      </c>
+      <c r="H90" t="s">
+        <v>590</v>
+      </c>
+      <c r="I90" t="s">
+        <v>591</v>
+      </c>
+      <c r="J90" t="s">
+        <v>592</v>
+      </c>
+      <c r="K90" t="s">
+        <v>593</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="S90">
+        <v>0</v>
+      </c>
+      <c r="T90">
+        <v>0</v>
+      </c>
+      <c r="W90">
+        <v>2</v>
+      </c>
+      <c r="X90">
+        <v>4</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>594</v>
+      </c>
+      <c r="AA90" t="s">
+        <v>595</v>
+      </c>
+      <c r="AB90" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC90" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="91" spans="1:30">
+      <c r="A91">
+        <v>3626796</v>
+      </c>
+      <c r="B91">
+        <v>2422</v>
+      </c>
+      <c r="C91">
+        <v>42</v>
+      </c>
+      <c r="D91">
+        <v>4</v>
+      </c>
+      <c r="E91">
+        <v>15</v>
+      </c>
+      <c r="F91">
+        <v>10</v>
+      </c>
+      <c r="G91">
+        <v>2026</v>
+      </c>
+      <c r="H91" t="s">
+        <v>596</v>
+      </c>
+      <c r="I91" t="s">
+        <v>597</v>
+      </c>
+      <c r="J91" t="s">
+        <v>598</v>
+      </c>
+      <c r="K91" t="s">
+        <v>599</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="S91">
+        <v>0</v>
+      </c>
+      <c r="T91">
+        <v>0</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>600</v>
+      </c>
+      <c r="AA91" t="s">
+        <v>601</v>
+      </c>
+      <c r="AB91" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC91" t="s">
+        <v>601</v>
       </c>
     </row>
   </sheetData>
